--- a/2D_Assets_digging/Storage_Assets_list.xlsx
+++ b/2D_Assets_digging/Storage_Assets_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wiwil\PZK\2D_Assets_digging\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5021EFEA-89D9-4B08-98EB-D482DE242E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A0BF39-FF98-47CB-AC47-CC17C62BF438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{66510CA7-CE23-4D88-8BD8-F76CB7A31B82}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{66510CA7-CE23-4D88-8BD8-F76CB7A31B82}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -406,7 +406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -414,31 +414,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -460,6 +440,25 @@
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -474,15 +473,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{394266AA-800B-47ED-960B-1A8E4C910DA1}" name="Tableau1" displayName="Tableau1" ref="A1:F64" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{394266AA-800B-47ED-960B-1A8E4C910DA1}" name="Tableau1" displayName="Tableau1" ref="A1:F64" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:F64" xr:uid="{394266AA-800B-47ED-960B-1A8E4C910DA1}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F64">
+    <sortCondition ref="B1:B64"/>
+  </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7169E61F-2BE0-4611-9484-C3FA7760C773}" name="Nom de l'objet" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{D8A9F5F5-6F13-4E58-BD26-302CE0260EC8}" name="Zone de spawn la plus logique" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{676A49B9-B321-4E84-8630-3BDB951F7FC3}" name="Type" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{85A5BD6E-EDC6-4FA5-B33D-1F6A9221D98E}" name="Image 2D ?" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{5AA4E991-501B-4939-BB62-2573209AFEB3}" name="Asset 3D ?" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{DF162DF5-7BC6-4535-95D2-D493F0EEA021}" name="Prépa blend/Fbx" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{7169E61F-2BE0-4611-9484-C3FA7760C773}" name="Nom de l'objet" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{D8A9F5F5-6F13-4E58-BD26-302CE0260EC8}" name="Zone de spawn la plus logique" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{676A49B9-B321-4E84-8630-3BDB951F7FC3}" name="Type" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{85A5BD6E-EDC6-4FA5-B33D-1F6A9221D98E}" name="Image 2D ?" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{5AA4E991-501B-4939-BB62-2573209AFEB3}" name="Asset 3D ?" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{DF162DF5-7BC6-4535-95D2-D493F0EEA021}" name="Prépa blend/Fbx" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -838,13 +840,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -852,10 +854,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>8</v>
@@ -866,13 +868,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -880,13 +882,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -894,10 +896,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>8</v>
@@ -908,13 +910,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -922,13 +924,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -936,10 +938,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>8</v>
@@ -950,10 +952,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>8</v>
@@ -964,13 +966,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -978,13 +980,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -992,10 +994,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>8</v>
@@ -1006,13 +1008,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -1020,13 +1022,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -1034,13 +1036,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -1048,10 +1050,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>8</v>
@@ -1062,10 +1064,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>8</v>
@@ -1076,10 +1078,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>8</v>
@@ -1090,10 +1092,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>8</v>
@@ -1104,10 +1106,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>8</v>
@@ -1118,10 +1120,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>8</v>
@@ -1132,10 +1134,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>8</v>
@@ -1146,10 +1148,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>8</v>
@@ -1160,10 +1162,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>8</v>
@@ -1174,10 +1176,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>8</v>
@@ -1188,10 +1190,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>8</v>
@@ -1202,13 +1204,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -1216,10 +1218,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>8</v>
@@ -1230,24 +1232,22 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>8</v>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>8</v>
@@ -1272,7 +1272,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>50</v>
@@ -1286,10 +1286,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>8</v>
@@ -1300,13 +1300,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -1314,13 +1314,13 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>62</v>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>62</v>
@@ -1356,13 +1356,13 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -1370,13 +1370,13 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
@@ -1384,13 +1384,13 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
@@ -1398,13 +1398,13 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>74</v>
+        <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>62</v>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>62</v>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>62</v>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>62</v>
@@ -1468,10 +1468,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>62</v>
@@ -1482,10 +1482,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>62</v>
@@ -1496,13 +1496,13 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -1510,10 +1510,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>62</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>7</v>
+        <v>107</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>62</v>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>62</v>
@@ -1552,13 +1552,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>62</v>
@@ -1594,13 +1594,13 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
@@ -1608,13 +1608,13 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>62</v>
@@ -1636,10 +1636,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>62</v>
@@ -1650,13 +1650,13 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
@@ -1664,7 +1664,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>102</v>
@@ -1678,7 +1678,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>102</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>62</v>
@@ -1706,17 +1706,17 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D64" s="2"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
